--- a/docs/program/RKA SDIT 2.xlsx
+++ b/docs/program/RKA SDIT 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Download\Laporan Program Pesantren\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Download\Tugas Akhir\Smart_Santri\smart_santri\docs\program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78C6CEC-3EB9-4012-8D67-FF409859C9D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CD1230-AAEB-4F59-8BEE-AA21873E6117}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5FC1093-13DE-40B7-AE57-7A5B093155AA}"/>
   </bookViews>
@@ -1516,12 +1516,6 @@
     <t>ISI</t>
   </si>
   <si>
-    <t>PROSES</t>
-  </si>
-  <si>
-    <t>PENDIDIK DAN TENAGA KEPENDIDIKAN</t>
-  </si>
-  <si>
     <t>PENGEMBANGAN SARANA DAN PRASARANA</t>
   </si>
   <si>
@@ -1532,6 +1526,12 @@
   </si>
   <si>
     <t>PENGEMBANGAN PENILAIAN</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN PROSES</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN PENDIDIK DAN TENAGA KEPENDIDIKAN</t>
   </si>
 </sst>
 </file>
@@ -1609,11 +1609,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1966,10 +1966,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1989,8 +1989,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
@@ -2008,8 +2008,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
@@ -2027,8 +2027,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
@@ -2046,10 +2046,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -2069,8 +2069,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
@@ -2088,8 +2088,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
@@ -2107,8 +2107,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="5" t="s">
         <v>35</v>
       </c>
@@ -2126,8 +2126,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="5" t="s">
         <v>37</v>
       </c>
@@ -2145,8 +2145,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="5" t="s">
         <v>39</v>
       </c>
@@ -2164,8 +2164,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="5" t="s">
         <v>41</v>
       </c>
@@ -2183,8 +2183,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="5" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2202,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="5" t="s">
         <v>47</v>
       </c>
@@ -2221,8 +2221,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="5" t="s">
         <v>49</v>
       </c>
@@ -2240,8 +2240,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -2261,8 +2261,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="5" t="s">
         <v>54</v>
       </c>
@@ -2280,8 +2280,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="5" t="s">
         <v>57</v>
       </c>
@@ -2299,8 +2299,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="5" t="s">
         <v>60</v>
       </c>
@@ -2318,8 +2318,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="5" t="s">
         <v>63</v>
       </c>
@@ -2337,8 +2337,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
@@ -2356,8 +2356,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="5" t="s">
         <v>69</v>
       </c>
@@ -2375,8 +2375,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="5" t="s">
         <v>72</v>
       </c>
@@ -2394,8 +2394,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
       <c r="C24" s="5" t="s">
         <v>75</v>
       </c>
@@ -2413,8 +2413,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="5" t="s">
         <v>78</v>
       </c>
@@ -2432,10 +2432,10 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="A26" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -2455,8 +2455,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="5" t="s">
         <v>85</v>
       </c>
@@ -2474,8 +2474,8 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="5" t="s">
         <v>87</v>
       </c>
@@ -2493,8 +2493,8 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="5" t="s">
         <v>89</v>
       </c>
@@ -2512,8 +2512,8 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="5" t="s">
         <v>91</v>
       </c>
@@ -2531,8 +2531,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="5" t="s">
         <v>93</v>
       </c>
@@ -2550,8 +2550,8 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="5" t="s">
         <v>96</v>
       </c>
@@ -2569,8 +2569,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="7" t="s">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8" t="s">
         <v>98</v>
       </c>
       <c r="C33" s="5" t="s">
@@ -2590,8 +2590,8 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="7"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
       <c r="C34" s="5" t="s">
         <v>103</v>
       </c>
@@ -2609,8 +2609,8 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="5" t="s">
         <v>106</v>
       </c>
@@ -2628,8 +2628,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="7"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="5" t="s">
         <v>108</v>
       </c>
@@ -2647,8 +2647,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="7"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="5" t="s">
         <v>111</v>
       </c>
@@ -2666,8 +2666,8 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="7"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="5" t="s">
         <v>114</v>
       </c>
@@ -2685,8 +2685,8 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="5" t="s">
         <v>116</v>
       </c>
@@ -2704,8 +2704,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="5" t="s">
         <v>118</v>
       </c>
@@ -2723,8 +2723,8 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="7"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="5" t="s">
         <v>120</v>
       </c>
@@ -2742,8 +2742,8 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="7"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="8"/>
       <c r="C42" s="5" t="s">
         <v>123</v>
       </c>
@@ -2761,8 +2761,8 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="5" t="s">
         <v>126</v>
       </c>
@@ -2780,8 +2780,8 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="5" t="s">
         <v>129</v>
       </c>
@@ -2799,8 +2799,8 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="7"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="5" t="s">
         <v>131</v>
       </c>
@@ -2818,8 +2818,8 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="7"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="5" t="s">
         <v>135</v>
       </c>
@@ -2837,8 +2837,8 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="7"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="5" t="s">
         <v>137</v>
       </c>
@@ -2856,8 +2856,8 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="5" t="s">
         <v>139</v>
       </c>
@@ -2875,8 +2875,8 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="7"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="8"/>
       <c r="C49" s="5" t="s">
         <v>142</v>
       </c>
@@ -2894,8 +2894,8 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="7"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="5" t="s">
         <v>145</v>
       </c>
@@ -2913,8 +2913,8 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="5" t="s">
         <v>148</v>
       </c>
@@ -2932,8 +2932,8 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="7"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="8"/>
       <c r="C52" s="5" t="s">
         <v>151</v>
       </c>
@@ -2951,8 +2951,8 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="7"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="5" t="s">
         <v>154</v>
       </c>
@@ -2970,8 +2970,8 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="7"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="8"/>
       <c r="C54" s="5" t="s">
         <v>156</v>
       </c>
@@ -2989,8 +2989,8 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="8"/>
       <c r="C55" s="5" t="s">
         <v>159</v>
       </c>
@@ -3008,8 +3008,8 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
       <c r="C56" s="5" t="s">
         <v>162</v>
       </c>
@@ -3027,8 +3027,8 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="7" t="s">
+      <c r="A57" s="7"/>
+      <c r="B57" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C57" s="5" t="s">
@@ -3048,8 +3048,8 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="8"/>
-      <c r="B58" s="7"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="8"/>
       <c r="C58" s="5" t="s">
         <v>168</v>
       </c>
@@ -3067,8 +3067,8 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="8"/>
-      <c r="B59" s="7"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="8"/>
       <c r="C59" s="5" t="s">
         <v>170</v>
       </c>
@@ -3086,8 +3086,8 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="8"/>
       <c r="C60" s="5" t="s">
         <v>172</v>
       </c>
@@ -3105,8 +3105,8 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="8"/>
-      <c r="B61" s="7"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="8"/>
       <c r="C61" s="5" t="s">
         <v>174</v>
       </c>
@@ -3124,8 +3124,8 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="8"/>
-      <c r="B62" s="7"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="8"/>
       <c r="C62" s="5" t="s">
         <v>176</v>
       </c>
@@ -3143,8 +3143,8 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="7"/>
+      <c r="A63" s="7"/>
+      <c r="B63" s="8"/>
       <c r="C63" s="5" t="s">
         <v>178</v>
       </c>
@@ -3162,8 +3162,8 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
-      <c r="B64" s="7"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
       <c r="C64" s="5" t="s">
         <v>180</v>
       </c>
@@ -3181,8 +3181,8 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="7"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="8"/>
       <c r="C65" s="5" t="s">
         <v>182</v>
       </c>
@@ -3200,8 +3200,8 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="7"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="5" t="s">
         <v>184</v>
       </c>
@@ -3219,8 +3219,8 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="8"/>
-      <c r="B67" s="7"/>
+      <c r="A67" s="7"/>
+      <c r="B67" s="8"/>
       <c r="C67" s="5" t="s">
         <v>187</v>
       </c>
@@ -3238,8 +3238,8 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="7"/>
+      <c r="A68" s="7"/>
+      <c r="B68" s="8"/>
       <c r="C68" s="5" t="s">
         <v>189</v>
       </c>
@@ -3257,8 +3257,8 @@
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="8"/>
-      <c r="B69" s="7"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="8"/>
       <c r="C69" s="5" t="s">
         <v>192</v>
       </c>
@@ -3276,8 +3276,8 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="8"/>
-      <c r="B70" s="7"/>
+      <c r="A70" s="7"/>
+      <c r="B70" s="8"/>
       <c r="C70" s="5" t="s">
         <v>194</v>
       </c>
@@ -3295,8 +3295,8 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="8"/>
-      <c r="B71" s="7" t="s">
+      <c r="A71" s="7"/>
+      <c r="B71" s="8" t="s">
         <v>196</v>
       </c>
       <c r="C71" s="5" t="s">
@@ -3316,8 +3316,8 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="8"/>
-      <c r="B72" s="7"/>
+      <c r="A72" s="7"/>
+      <c r="B72" s="8"/>
       <c r="C72" s="5" t="s">
         <v>199</v>
       </c>
@@ -3335,8 +3335,8 @@
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="8"/>
-      <c r="B73" s="7"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
       <c r="C73" s="5" t="s">
         <v>201</v>
       </c>
@@ -3354,8 +3354,8 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="8"/>
-      <c r="B74" s="7" t="s">
+      <c r="A74" s="7"/>
+      <c r="B74" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C74" s="5" t="s">
@@ -3375,8 +3375,8 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="8"/>
-      <c r="B75" s="7"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="8"/>
       <c r="C75" s="5" t="s">
         <v>206</v>
       </c>
@@ -3394,8 +3394,8 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="8"/>
-      <c r="B76" s="7"/>
+      <c r="A76" s="7"/>
+      <c r="B76" s="8"/>
       <c r="C76" s="5" t="s">
         <v>208</v>
       </c>
@@ -3413,8 +3413,8 @@
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="8"/>
-      <c r="B77" s="7"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="5" t="s">
         <v>210</v>
       </c>
@@ -3432,8 +3432,8 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="8"/>
-      <c r="B78" s="7"/>
+      <c r="A78" s="7"/>
+      <c r="B78" s="8"/>
       <c r="C78" s="5" t="s">
         <v>212</v>
       </c>
@@ -3451,8 +3451,8 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="8"/>
-      <c r="B79" s="7"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="8"/>
       <c r="C79" s="5" t="s">
         <v>214</v>
       </c>
@@ -3470,8 +3470,8 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="8"/>
-      <c r="B80" s="7" t="s">
+      <c r="A80" s="7"/>
+      <c r="B80" s="8" t="s">
         <v>217</v>
       </c>
       <c r="C80" s="5" t="s">
@@ -3491,8 +3491,8 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="8"/>
-      <c r="B81" s="7"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="8"/>
       <c r="C81" s="5" t="s">
         <v>221</v>
       </c>
@@ -3510,10 +3510,10 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="B82" s="7" t="s">
+      <c r="A82" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>224</v>
       </c>
       <c r="C82" s="5" t="s">
@@ -3533,8 +3533,8 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="8"/>
-      <c r="B83" s="7"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="8"/>
       <c r="C83" s="5" t="s">
         <v>228</v>
       </c>
@@ -3552,8 +3552,8 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="8"/>
-      <c r="B84" s="7"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="8"/>
       <c r="C84" s="5" t="s">
         <v>231</v>
       </c>
@@ -3571,8 +3571,8 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="8"/>
-      <c r="B85" s="7"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="8"/>
       <c r="C85" s="5" t="s">
         <v>232</v>
       </c>
@@ -3590,8 +3590,8 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="8"/>
-      <c r="B86" s="7"/>
+      <c r="A86" s="7"/>
+      <c r="B86" s="8"/>
       <c r="C86" s="5" t="s">
         <v>234</v>
       </c>
@@ -3609,8 +3609,8 @@
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="8"/>
-      <c r="B87" s="7"/>
+      <c r="A87" s="7"/>
+      <c r="B87" s="8"/>
       <c r="C87" s="5" t="s">
         <v>237</v>
       </c>
@@ -3628,8 +3628,8 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="8"/>
-      <c r="B88" s="7"/>
+      <c r="A88" s="7"/>
+      <c r="B88" s="8"/>
       <c r="C88" s="5" t="s">
         <v>239</v>
       </c>
@@ -3647,8 +3647,8 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="8"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
       <c r="C89" s="5" t="s">
         <v>241</v>
       </c>
@@ -3666,8 +3666,8 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="8"/>
-      <c r="B90" s="7"/>
+      <c r="A90" s="7"/>
+      <c r="B90" s="8"/>
       <c r="C90" s="5" t="s">
         <v>243</v>
       </c>
@@ -3685,8 +3685,8 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="8"/>
-      <c r="B91" s="7"/>
+      <c r="A91" s="7"/>
+      <c r="B91" s="8"/>
       <c r="C91" s="5" t="s">
         <v>245</v>
       </c>
@@ -3704,8 +3704,8 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="8"/>
-      <c r="B92" s="7"/>
+      <c r="A92" s="7"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="5" t="s">
         <v>247</v>
       </c>
@@ -3723,8 +3723,8 @@
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="8"/>
-      <c r="B93" s="7"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="5" t="s">
         <v>248</v>
       </c>
@@ -3742,8 +3742,8 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="8"/>
-      <c r="B94" s="7"/>
+      <c r="A94" s="7"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="5" t="s">
         <v>250</v>
       </c>
@@ -3761,8 +3761,8 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="8"/>
-      <c r="B95" s="7"/>
+      <c r="A95" s="7"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="5" t="s">
         <v>253</v>
       </c>
@@ -3780,10 +3780,10 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="B96" s="7" t="s">
+      <c r="A96" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B96" s="8" t="s">
         <v>255</v>
       </c>
       <c r="C96" s="5" t="s">
@@ -3803,8 +3803,8 @@
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="8"/>
-      <c r="B97" s="7"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="8"/>
       <c r="C97" s="5" t="s">
         <v>258</v>
       </c>
@@ -3822,8 +3822,8 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="8"/>
-      <c r="B98" s="7"/>
+      <c r="A98" s="7"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="5" t="s">
         <v>260</v>
       </c>
@@ -3841,8 +3841,8 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="8"/>
-      <c r="B99" s="7"/>
+      <c r="A99" s="7"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="5" t="s">
         <v>262</v>
       </c>
@@ -3860,8 +3860,8 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="8"/>
-      <c r="B100" s="7"/>
+      <c r="A100" s="7"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="5" t="s">
         <v>265</v>
       </c>
@@ -3879,8 +3879,8 @@
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="8"/>
-      <c r="B101" s="7"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="5" t="s">
         <v>267</v>
       </c>
@@ -3898,8 +3898,8 @@
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="8"/>
-      <c r="B102" s="7"/>
+      <c r="A102" s="7"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="5" t="s">
         <v>270</v>
       </c>
@@ -3917,8 +3917,8 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="8"/>
-      <c r="B103" s="7"/>
+      <c r="A103" s="7"/>
+      <c r="B103" s="8"/>
       <c r="C103" s="5" t="s">
         <v>272</v>
       </c>
@@ -3936,8 +3936,8 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="8"/>
-      <c r="B104" s="7" t="s">
+      <c r="A104" s="7"/>
+      <c r="B104" s="8" t="s">
         <v>274</v>
       </c>
       <c r="C104" s="5" t="s">
@@ -3957,8 +3957,8 @@
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="8"/>
-      <c r="B105" s="7"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="8"/>
       <c r="C105" s="5" t="s">
         <v>277</v>
       </c>
@@ -3976,8 +3976,8 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="8"/>
-      <c r="B106" s="7"/>
+      <c r="A106" s="7"/>
+      <c r="B106" s="8"/>
       <c r="C106" s="5" t="s">
         <v>279</v>
       </c>
@@ -3995,8 +3995,8 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="8"/>
-      <c r="B107" s="7"/>
+      <c r="A107" s="7"/>
+      <c r="B107" s="8"/>
       <c r="C107" s="5" t="s">
         <v>281</v>
       </c>
@@ -4014,8 +4014,8 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="8"/>
-      <c r="B108" s="7"/>
+      <c r="A108" s="7"/>
+      <c r="B108" s="8"/>
       <c r="C108" s="5" t="s">
         <v>283</v>
       </c>
@@ -4033,8 +4033,8 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="8"/>
-      <c r="B109" s="7"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="8"/>
       <c r="C109" s="5" t="s">
         <v>285</v>
       </c>
@@ -4052,8 +4052,8 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="8"/>
-      <c r="B110" s="7"/>
+      <c r="A110" s="7"/>
+      <c r="B110" s="8"/>
       <c r="C110" s="5" t="s">
         <v>287</v>
       </c>
@@ -4071,8 +4071,8 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="8"/>
-      <c r="B111" s="7"/>
+      <c r="A111" s="7"/>
+      <c r="B111" s="8"/>
       <c r="C111" s="5" t="s">
         <v>289</v>
       </c>
@@ -4090,8 +4090,8 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="8"/>
-      <c r="B112" s="7" t="s">
+      <c r="A112" s="7"/>
+      <c r="B112" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C112" s="5" t="s">
@@ -4111,8 +4111,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="8"/>
-      <c r="B113" s="7"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="8"/>
       <c r="C113" s="5" t="s">
         <v>294</v>
       </c>
@@ -4130,8 +4130,8 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="8"/>
-      <c r="B114" s="7"/>
+      <c r="A114" s="7"/>
+      <c r="B114" s="8"/>
       <c r="C114" s="5" t="s">
         <v>296</v>
       </c>
@@ -4149,8 +4149,8 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="8"/>
-      <c r="B115" s="7"/>
+      <c r="A115" s="7"/>
+      <c r="B115" s="8"/>
       <c r="C115" s="5" t="s">
         <v>298</v>
       </c>
@@ -4168,8 +4168,8 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="8"/>
-      <c r="B116" s="7"/>
+      <c r="A116" s="7"/>
+      <c r="B116" s="8"/>
       <c r="C116" s="5" t="s">
         <v>300</v>
       </c>
@@ -4187,8 +4187,8 @@
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="8"/>
-      <c r="B117" s="7"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="8"/>
       <c r="C117" s="5" t="s">
         <v>302</v>
       </c>
@@ -4206,8 +4206,8 @@
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="8"/>
-      <c r="B118" s="7"/>
+      <c r="A118" s="7"/>
+      <c r="B118" s="8"/>
       <c r="C118" s="5" t="s">
         <v>304</v>
       </c>
@@ -4225,8 +4225,8 @@
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="8"/>
-      <c r="B119" s="7"/>
+      <c r="A119" s="7"/>
+      <c r="B119" s="8"/>
       <c r="C119" s="5" t="s">
         <v>306</v>
       </c>
@@ -4244,8 +4244,8 @@
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="8"/>
-      <c r="B120" s="7"/>
+      <c r="A120" s="7"/>
+      <c r="B120" s="8"/>
       <c r="C120" s="5" t="s">
         <v>308</v>
       </c>
@@ -4263,8 +4263,8 @@
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="8"/>
-      <c r="B121" s="7"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="8"/>
       <c r="C121" s="5" t="s">
         <v>310</v>
       </c>
@@ -4282,8 +4282,8 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="8"/>
-      <c r="B122" s="7"/>
+      <c r="A122" s="7"/>
+      <c r="B122" s="8"/>
       <c r="C122" s="5" t="s">
         <v>312</v>
       </c>
@@ -4301,8 +4301,8 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="8"/>
-      <c r="B123" s="7"/>
+      <c r="A123" s="7"/>
+      <c r="B123" s="8"/>
       <c r="C123" s="5" t="s">
         <v>314</v>
       </c>
@@ -4320,8 +4320,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="8"/>
-      <c r="B124" s="7"/>
+      <c r="A124" s="7"/>
+      <c r="B124" s="8"/>
       <c r="C124" s="5" t="s">
         <v>317</v>
       </c>
@@ -4339,8 +4339,8 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="8"/>
-      <c r="B125" s="7" t="s">
+      <c r="A125" s="7"/>
+      <c r="B125" s="8" t="s">
         <v>319</v>
       </c>
       <c r="C125" s="5" t="s">
@@ -4360,8 +4360,8 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="8"/>
-      <c r="B126" s="7"/>
+      <c r="A126" s="7"/>
+      <c r="B126" s="8"/>
       <c r="C126" s="5" t="s">
         <v>322</v>
       </c>
@@ -4379,8 +4379,8 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="8"/>
-      <c r="B127" s="7"/>
+      <c r="A127" s="7"/>
+      <c r="B127" s="8"/>
       <c r="C127" s="5" t="s">
         <v>325</v>
       </c>
@@ -4398,7 +4398,7 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="8"/>
+      <c r="A128" s="7"/>
       <c r="B128" s="5" t="s">
         <v>327</v>
       </c>
@@ -4419,8 +4419,8 @@
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="8"/>
-      <c r="B129" s="7" t="s">
+      <c r="A129" s="7"/>
+      <c r="B129" s="8" t="s">
         <v>330</v>
       </c>
       <c r="C129" s="5" t="s">
@@ -4440,8 +4440,8 @@
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="8"/>
-      <c r="B130" s="7"/>
+      <c r="A130" s="7"/>
+      <c r="B130" s="8"/>
       <c r="C130" s="5" t="s">
         <v>333</v>
       </c>
@@ -4459,8 +4459,8 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="8"/>
-      <c r="B131" s="7"/>
+      <c r="A131" s="7"/>
+      <c r="B131" s="8"/>
       <c r="C131" s="5" t="s">
         <v>335</v>
       </c>
@@ -4478,8 +4478,8 @@
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="8"/>
-      <c r="B132" s="7"/>
+      <c r="A132" s="7"/>
+      <c r="B132" s="8"/>
       <c r="C132" s="5" t="s">
         <v>337</v>
       </c>
@@ -4497,8 +4497,8 @@
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="8"/>
-      <c r="B133" s="7"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="8"/>
       <c r="C133" s="5" t="s">
         <v>339</v>
       </c>
@@ -4516,8 +4516,8 @@
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="8"/>
-      <c r="B134" s="7"/>
+      <c r="A134" s="7"/>
+      <c r="B134" s="8"/>
       <c r="C134" s="5" t="s">
         <v>341</v>
       </c>
@@ -4535,8 +4535,8 @@
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="8"/>
-      <c r="B135" s="7"/>
+      <c r="A135" s="7"/>
+      <c r="B135" s="8"/>
       <c r="C135" s="5" t="s">
         <v>343</v>
       </c>
@@ -4554,8 +4554,8 @@
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="8"/>
-      <c r="B136" s="7"/>
+      <c r="A136" s="7"/>
+      <c r="B136" s="8"/>
       <c r="C136" s="5" t="s">
         <v>345</v>
       </c>
@@ -4573,8 +4573,8 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="8"/>
-      <c r="B137" s="7"/>
+      <c r="A137" s="7"/>
+      <c r="B137" s="8"/>
       <c r="C137" s="5" t="s">
         <v>347</v>
       </c>
@@ -4592,8 +4592,8 @@
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="8"/>
-      <c r="B138" s="7"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="8"/>
       <c r="C138" s="5" t="s">
         <v>349</v>
       </c>
@@ -4611,8 +4611,8 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="8"/>
-      <c r="B139" s="7"/>
+      <c r="A139" s="7"/>
+      <c r="B139" s="8"/>
       <c r="C139" s="5" t="s">
         <v>351</v>
       </c>
@@ -4630,7 +4630,7 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="8"/>
+      <c r="A140" s="7"/>
       <c r="B140" s="5" t="s">
         <v>353</v>
       </c>
@@ -4651,10 +4651,10 @@
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="B141" s="7" t="s">
+      <c r="A141" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B141" s="8" t="s">
         <v>356</v>
       </c>
       <c r="C141" s="5" t="s">
@@ -4674,8 +4674,8 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="8"/>
-      <c r="B142" s="7"/>
+      <c r="A142" s="7"/>
+      <c r="B142" s="8"/>
       <c r="C142" s="5" t="s">
         <v>359</v>
       </c>
@@ -4693,8 +4693,8 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="8"/>
-      <c r="B143" s="7"/>
+      <c r="A143" s="7"/>
+      <c r="B143" s="8"/>
       <c r="C143" s="5" t="s">
         <v>361</v>
       </c>
@@ -4712,8 +4712,8 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="8"/>
-      <c r="B144" s="7" t="s">
+      <c r="A144" s="7"/>
+      <c r="B144" s="8" t="s">
         <v>363</v>
       </c>
       <c r="C144" s="5" t="s">
@@ -4733,8 +4733,8 @@
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="8"/>
-      <c r="B145" s="7"/>
+      <c r="A145" s="7"/>
+      <c r="B145" s="8"/>
       <c r="C145" s="5" t="s">
         <v>367</v>
       </c>
@@ -4752,8 +4752,8 @@
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="8"/>
-      <c r="B146" s="7" t="s">
+      <c r="A146" s="7"/>
+      <c r="B146" s="8" t="s">
         <v>369</v>
       </c>
       <c r="C146" s="5" t="s">
@@ -4773,8 +4773,8 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="8"/>
-      <c r="B147" s="7"/>
+      <c r="A147" s="7"/>
+      <c r="B147" s="8"/>
       <c r="C147" s="5" t="s">
         <v>372</v>
       </c>
@@ -4792,8 +4792,8 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="8"/>
-      <c r="B148" s="7"/>
+      <c r="A148" s="7"/>
+      <c r="B148" s="8"/>
       <c r="C148" s="5" t="s">
         <v>374</v>
       </c>
@@ -4811,8 +4811,8 @@
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="8"/>
-      <c r="B149" s="7"/>
+      <c r="A149" s="7"/>
+      <c r="B149" s="8"/>
       <c r="C149" s="5" t="s">
         <v>376</v>
       </c>
@@ -4830,8 +4830,8 @@
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="8"/>
-      <c r="B150" s="7"/>
+      <c r="A150" s="7"/>
+      <c r="B150" s="8"/>
       <c r="C150" s="5" t="s">
         <v>377</v>
       </c>
@@ -4849,8 +4849,8 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="8"/>
-      <c r="B151" s="7"/>
+      <c r="A151" s="7"/>
+      <c r="B151" s="8"/>
       <c r="C151" s="5" t="s">
         <v>378</v>
       </c>
@@ -4868,8 +4868,8 @@
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="8"/>
-      <c r="B152" s="7"/>
+      <c r="A152" s="7"/>
+      <c r="B152" s="8"/>
       <c r="C152" s="5" t="s">
         <v>380</v>
       </c>
@@ -4887,8 +4887,8 @@
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="8"/>
-      <c r="B153" s="7"/>
+      <c r="A153" s="7"/>
+      <c r="B153" s="8"/>
       <c r="C153" s="5" t="s">
         <v>382</v>
       </c>
@@ -4906,8 +4906,8 @@
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="8"/>
-      <c r="B154" s="7" t="s">
+      <c r="A154" s="7"/>
+      <c r="B154" s="8" t="s">
         <v>383</v>
       </c>
       <c r="C154" s="5" t="s">
@@ -4927,8 +4927,8 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="8"/>
-      <c r="B155" s="7"/>
+      <c r="A155" s="7"/>
+      <c r="B155" s="8"/>
       <c r="C155" s="5" t="s">
         <v>386</v>
       </c>
@@ -4946,8 +4946,8 @@
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="8"/>
-      <c r="B156" s="7" t="s">
+      <c r="A156" s="7"/>
+      <c r="B156" s="8" t="s">
         <v>388</v>
       </c>
       <c r="C156" s="5" t="s">
@@ -4967,8 +4967,8 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="8"/>
-      <c r="B157" s="7"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="8"/>
       <c r="C157" s="5" t="s">
         <v>391</v>
       </c>
@@ -4986,8 +4986,8 @@
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="8"/>
-      <c r="B158" s="7"/>
+      <c r="A158" s="7"/>
+      <c r="B158" s="8"/>
       <c r="C158" s="5" t="s">
         <v>393</v>
       </c>
@@ -5005,8 +5005,8 @@
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="8"/>
-      <c r="B159" s="7" t="s">
+      <c r="A159" s="7"/>
+      <c r="B159" s="8" t="s">
         <v>395</v>
       </c>
       <c r="C159" s="5" t="s">
@@ -5026,8 +5026,8 @@
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="8"/>
-      <c r="B160" s="7"/>
+      <c r="A160" s="7"/>
+      <c r="B160" s="8"/>
       <c r="C160" s="5" t="s">
         <v>398</v>
       </c>
@@ -5045,7 +5045,7 @@
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="8"/>
+      <c r="A161" s="7"/>
       <c r="B161" s="5" t="s">
         <v>400</v>
       </c>
@@ -5066,7 +5066,7 @@
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="8"/>
+      <c r="A162" s="7"/>
       <c r="B162" s="5" t="s">
         <v>403</v>
       </c>
@@ -5087,7 +5087,7 @@
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="8"/>
+      <c r="A163" s="7"/>
       <c r="B163" s="5" t="s">
         <v>406</v>
       </c>
@@ -5108,7 +5108,7 @@
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="8"/>
+      <c r="A164" s="7"/>
       <c r="B164" s="5" t="s">
         <v>409</v>
       </c>
@@ -5129,10 +5129,10 @@
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="B165" s="7" t="s">
+      <c r="A165" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B165" s="8" t="s">
         <v>412</v>
       </c>
       <c r="C165" s="5" t="s">
@@ -5152,8 +5152,8 @@
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="8"/>
-      <c r="B166" s="7"/>
+      <c r="A166" s="7"/>
+      <c r="B166" s="8"/>
       <c r="C166" s="5" t="s">
         <v>415</v>
       </c>
@@ -5171,8 +5171,8 @@
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="8"/>
-      <c r="B167" s="7"/>
+      <c r="A167" s="7"/>
+      <c r="B167" s="8"/>
       <c r="C167" s="5" t="s">
         <v>417</v>
       </c>
@@ -5190,8 +5190,8 @@
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="8"/>
-      <c r="B168" s="7"/>
+      <c r="A168" s="7"/>
+      <c r="B168" s="8"/>
       <c r="C168" s="5" t="s">
         <v>419</v>
       </c>
@@ -5209,8 +5209,8 @@
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="8"/>
-      <c r="B169" s="7"/>
+      <c r="A169" s="7"/>
+      <c r="B169" s="8"/>
       <c r="C169" s="5" t="s">
         <v>421</v>
       </c>
@@ -5224,8 +5224,8 @@
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="8"/>
-      <c r="B170" s="7"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="8"/>
       <c r="C170" s="5" t="s">
         <v>423</v>
       </c>
@@ -5239,8 +5239,8 @@
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="8"/>
-      <c r="B171" s="7" t="s">
+      <c r="A171" s="7"/>
+      <c r="B171" s="8" t="s">
         <v>425</v>
       </c>
       <c r="C171" s="5" t="s">
@@ -5260,8 +5260,8 @@
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="8"/>
-      <c r="B172" s="7"/>
+      <c r="A172" s="7"/>
+      <c r="B172" s="8"/>
       <c r="C172" s="5" t="s">
         <v>428</v>
       </c>
@@ -5279,8 +5279,8 @@
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="8"/>
-      <c r="B173" s="7"/>
+      <c r="A173" s="7"/>
+      <c r="B173" s="8"/>
       <c r="C173" s="5" t="s">
         <v>430</v>
       </c>
@@ -5298,8 +5298,8 @@
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="8"/>
-      <c r="B174" s="7"/>
+      <c r="A174" s="7"/>
+      <c r="B174" s="8"/>
       <c r="C174" s="5" t="s">
         <v>432</v>
       </c>
@@ -5317,8 +5317,8 @@
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="8"/>
-      <c r="B175" s="7"/>
+      <c r="A175" s="7"/>
+      <c r="B175" s="8"/>
       <c r="C175" s="5" t="s">
         <v>434</v>
       </c>
@@ -5336,8 +5336,8 @@
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="8"/>
-      <c r="B176" s="7"/>
+      <c r="A176" s="7"/>
+      <c r="B176" s="8"/>
       <c r="C176" s="5" t="s">
         <v>436</v>
       </c>
@@ -5355,8 +5355,8 @@
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="8"/>
-      <c r="B177" s="7"/>
+      <c r="A177" s="7"/>
+      <c r="B177" s="8"/>
       <c r="C177" s="5" t="s">
         <v>438</v>
       </c>
@@ -5374,8 +5374,8 @@
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="8"/>
-      <c r="B178" s="7"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="8"/>
       <c r="C178" s="5" t="s">
         <v>440</v>
       </c>
@@ -5393,8 +5393,8 @@
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="8"/>
-      <c r="B179" s="7" t="s">
+      <c r="A179" s="7"/>
+      <c r="B179" s="8" t="s">
         <v>443</v>
       </c>
       <c r="C179" s="5" t="s">
@@ -5414,8 +5414,8 @@
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="8"/>
-      <c r="B180" s="7"/>
+      <c r="A180" s="7"/>
+      <c r="B180" s="8"/>
       <c r="C180" s="5" t="s">
         <v>446</v>
       </c>
@@ -5433,8 +5433,8 @@
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="8"/>
-      <c r="B181" s="7"/>
+      <c r="A181" s="7"/>
+      <c r="B181" s="8"/>
       <c r="C181" s="5" t="s">
         <v>448</v>
       </c>
@@ -5452,8 +5452,8 @@
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="8"/>
-      <c r="B182" s="7"/>
+      <c r="A182" s="7"/>
+      <c r="B182" s="8"/>
       <c r="C182" s="5" t="s">
         <v>450</v>
       </c>
@@ -5471,7 +5471,7 @@
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="8"/>
+      <c r="A183" s="7"/>
       <c r="B183" s="5" t="s">
         <v>452</v>
       </c>
@@ -5492,7 +5492,7 @@
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="8"/>
+      <c r="A184" s="7"/>
       <c r="B184" s="5" t="s">
         <v>455</v>
       </c>
@@ -5513,10 +5513,10 @@
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="B185" s="7" t="s">
+      <c r="A185" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="B185" s="8" t="s">
         <v>458</v>
       </c>
       <c r="C185" s="5" t="s">
@@ -5536,8 +5536,8 @@
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="8"/>
-      <c r="B186" s="7"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="8"/>
       <c r="C186" s="5" t="s">
         <v>461</v>
       </c>
@@ -5555,8 +5555,8 @@
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="8"/>
-      <c r="B187" s="7"/>
+      <c r="A187" s="7"/>
+      <c r="B187" s="8"/>
       <c r="C187" s="5" t="s">
         <v>463</v>
       </c>
@@ -5574,8 +5574,8 @@
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="8"/>
-      <c r="B188" s="7"/>
+      <c r="A188" s="7"/>
+      <c r="B188" s="8"/>
       <c r="C188" s="5" t="s">
         <v>465</v>
       </c>
@@ -5593,8 +5593,8 @@
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="8"/>
-      <c r="B189" s="7"/>
+      <c r="A189" s="7"/>
+      <c r="B189" s="8"/>
       <c r="C189" s="5" t="s">
         <v>467</v>
       </c>
@@ -5612,8 +5612,8 @@
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="8"/>
-      <c r="B190" s="7"/>
+      <c r="A190" s="7"/>
+      <c r="B190" s="8"/>
       <c r="C190" s="5" t="s">
         <v>469</v>
       </c>
@@ -5631,8 +5631,8 @@
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="8"/>
-      <c r="B191" s="7"/>
+      <c r="A191" s="7"/>
+      <c r="B191" s="8"/>
       <c r="C191" s="5" t="s">
         <v>470</v>
       </c>
@@ -5650,8 +5650,8 @@
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="8"/>
-      <c r="B192" s="7"/>
+      <c r="A192" s="7"/>
+      <c r="B192" s="8"/>
       <c r="C192" s="5" t="s">
         <v>472</v>
       </c>
@@ -5669,8 +5669,8 @@
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="8"/>
-      <c r="B193" s="7"/>
+      <c r="A193" s="7"/>
+      <c r="B193" s="8"/>
       <c r="C193" s="5" t="s">
         <v>474</v>
       </c>
@@ -5688,8 +5688,8 @@
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="8"/>
-      <c r="B194" s="7"/>
+      <c r="A194" s="7"/>
+      <c r="B194" s="8"/>
       <c r="C194" s="5" t="s">
         <v>476</v>
       </c>
@@ -5707,8 +5707,8 @@
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A195" s="8"/>
-      <c r="B195" s="7"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="8"/>
       <c r="C195" s="5" t="s">
         <v>478</v>
       </c>
@@ -5726,8 +5726,8 @@
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="8"/>
-      <c r="B196" s="7"/>
+      <c r="A196" s="7"/>
+      <c r="B196" s="8"/>
       <c r="C196" s="5" t="s">
         <v>480</v>
       </c>
@@ -5745,8 +5745,8 @@
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="8"/>
-      <c r="B197" s="7"/>
+      <c r="A197" s="7"/>
+      <c r="B197" s="8"/>
       <c r="C197" s="5" t="s">
         <v>482</v>
       </c>
@@ -5765,6 +5765,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="B185:B197"/>
+    <mergeCell ref="A185:A197"/>
+    <mergeCell ref="B156:B158"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="A141:A164"/>
+    <mergeCell ref="B165:B170"/>
+    <mergeCell ref="B171:B178"/>
+    <mergeCell ref="B179:B182"/>
+    <mergeCell ref="A165:A184"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="B129:B139"/>
+    <mergeCell ref="A96:A140"/>
+    <mergeCell ref="B141:B143"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="B146:B153"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B82:B95"/>
+    <mergeCell ref="B96:B103"/>
+    <mergeCell ref="A82:A95"/>
+    <mergeCell ref="B104:B111"/>
+    <mergeCell ref="B112:B124"/>
     <mergeCell ref="A26:A81"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
@@ -5777,27 +5798,6 @@
     <mergeCell ref="B71:B73"/>
     <mergeCell ref="B74:B79"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B82:B95"/>
-    <mergeCell ref="B96:B103"/>
-    <mergeCell ref="A82:A95"/>
-    <mergeCell ref="B104:B111"/>
-    <mergeCell ref="B112:B124"/>
-    <mergeCell ref="B129:B139"/>
-    <mergeCell ref="A96:A140"/>
-    <mergeCell ref="B141:B143"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="B146:B153"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B185:B197"/>
-    <mergeCell ref="A185:A197"/>
-    <mergeCell ref="B156:B158"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="A141:A164"/>
-    <mergeCell ref="B165:B170"/>
-    <mergeCell ref="B171:B178"/>
-    <mergeCell ref="B179:B182"/>
-    <mergeCell ref="A165:A184"/>
-    <mergeCell ref="B154:B155"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
